--- a/doc/MQTT scheme.xlsx
+++ b/doc/MQTT scheme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\INNO\INNO-Institute-for-Design-Engineering\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BEADB9D-BA84-4B3B-A755-6EDAB6D25429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD55436-1413-468E-AE9C-38C51006CA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="38">
   <si>
     <t>car/</t>
   </si>
@@ -78,12 +78,6 @@
     <t>Huidige snelheid van de auto</t>
   </si>
   <si>
-    <t>Angel</t>
-  </si>
-  <si>
-    <t>Huidige hoek van de wielen</t>
-  </si>
-  <si>
     <t>data/</t>
   </si>
   <si>
@@ -133,6 +127,18 @@
   </si>
   <si>
     <t>MagnetSensorR</t>
+  </si>
+  <si>
+    <t>car/{ident}/</t>
+  </si>
+  <si>
+    <t>CarB</t>
+  </si>
+  <si>
+    <t>CarC</t>
+  </si>
+  <si>
+    <t>CarA</t>
   </si>
 </sst>
 </file>
@@ -450,23 +456,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
         <v>2</v>
       </c>
@@ -477,7 +484,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
         <v>5</v>
       </c>
@@ -488,7 +495,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
         <v>8</v>
       </c>
@@ -496,10 +503,10 @@
         <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
         <v>10</v>
       </c>
@@ -510,23 +517,23 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="C8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
         <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="C9" t="s">
         <v>12</v>
       </c>
@@ -537,7 +544,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="C10" t="s">
         <v>15</v>
       </c>
@@ -548,69 +555,78 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="C11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
         <v>6</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="C13" t="s">
         <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="C14" t="s">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
         <v>24</v>
       </c>
-      <c r="D14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="L14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="M15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="C16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s">
         <v>13</v>
       </c>
       <c r="E16" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C17" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C17" t="s">
-        <v>35</v>
       </c>
       <c r="D17" t="s">
         <v>13</v>
@@ -618,16 +634,8 @@
       <c r="E17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="18" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C18" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" t="s">
-        <v>30</v>
+      <c r="M17" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/doc/MQTT scheme.xlsx
+++ b/doc/MQTT scheme.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\INNO\INNO-Institute-for-Design-Engineering\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD55436-1413-468E-AE9C-38C51006CA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62E60EBB-7F39-4195-AB38-780C59A027BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -640,5 +640,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>